--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,12 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rf0ddd04d7ce84f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体" sheetId="2" r:id="Ra073e724b10d445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高" sheetId="3" r:id="R0fec773a3bd74a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益" sheetId="4" r:id="Re9a864ae31404e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注" sheetId="5" r:id="R63b41db766b743ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR" sheetId="6" r:id="Rf54d402bdb994037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rcfb97edeee5d4f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R1e989b81a9fc4baf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R4f8cbb295fa84980"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R461e0abb93d34c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rb2d426add6664c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R8e4e205473914d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R5278f08d0c354494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R086acb5cfe854172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="Rde78ec81d6214568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rfb106c1610434092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R499619424c034ebe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,23 +32,23 @@
       <x:b/>
       <x:sz val="18"/>
       <x:color rgb="FF17325C"/>
-      <x:name val="Noto Sans JP"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF61728A"/>
-      <x:name val="Noto Sans JP"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Noto Sans JP"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF17325C"/>
-      <x:name val="Noto Sans JP"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -71,7 +76,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -92,18 +97,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -325,7 +318,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>会社名・通貨・表示単位・サブタイトル・カラーを一括指定します。</x:v>
+        <x:v>年度・四半期共通の会社設定。カラー、通貨、表示単位、サブタイトルを指定します。</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -345,14 +338,14 @@
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
         <x:v>setting</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>説明</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
@@ -362,13 +355,13 @@
       <x:c r="H4" s="2"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="17" t="str">
+      <x:c r="A5" s="14" t="str">
         <x:v>company_name</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="str">
+      <x:c r="B5" s="14" t="str">
         <x:v>サンプル株式会社</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
+      <x:c r="C5" s="14" t="str">
         <x:v>企業名</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
@@ -378,14 +371,14 @@
       <x:c r="H5" s="2"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="17" t="str">
+      <x:c r="A6" s="14" t="str">
         <x:v>note</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="str">
+      <x:c r="B6" s="14" t="str">
         <x:v>※ 最新期は会社予想</x:v>
       </x:c>
-      <x:c r="C6" s="17" t="str">
-        <x:v>全グラフ共通</x:v>
+      <x:c r="C6" s="14" t="str">
+        <x:v>共通注意書き</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -394,13 +387,13 @@
       <x:c r="H6" s="2"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="17" t="str">
+      <x:c r="A7" s="14" t="str">
         <x:v>input_currency</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="str">
+      <x:c r="B7" s="14" t="str">
         <x:v>JPY</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="str">
+      <x:c r="C7" s="14" t="str">
         <x:v>JPY/USD/EUR/CNY/DKK/KRW/NOK/SEK/CHF/TWD/HKD</x:v>
       </x:c>
       <x:c r="D7" s="2"/>
@@ -410,13 +403,13 @@
       <x:c r="H7" s="2"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="17" t="str">
+      <x:c r="A8" s="14" t="str">
         <x:v>display_unit</x:v>
       </x:c>
-      <x:c r="B8" s="17" t="str">
+      <x:c r="B8" s="14" t="str">
         <x:v>億円</x:v>
       </x:c>
-      <x:c r="C8" s="17" t="str">
+      <x:c r="C8" s="14" t="str">
         <x:v>表示単位</x:v>
       </x:c>
       <x:c r="D8" s="2"/>
@@ -426,13 +419,13 @@
       <x:c r="H8" s="2"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="17" t="str">
+      <x:c r="A9" s="14" t="str">
         <x:v>company_subtitle</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str">
+      <x:c r="B9" s="14" t="str">
         <x:v>売上高・営業利益・営業利益率の推移（円ベース）</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str">
+      <x:c r="C9" s="14" t="str">
         <x:v>会社全体</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
@@ -442,13 +435,13 @@
       <x:c r="H9" s="2"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="17" t="str">
+      <x:c r="A10" s="14" t="str">
         <x:v>revenue_color</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str">
+      <x:c r="B10" s="14" t="str">
         <x:v>#1675F8</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str">
+      <x:c r="C10" s="14" t="str">
         <x:v>売上高</x:v>
       </x:c>
       <x:c r="D10" s="2"/>
@@ -458,13 +451,13 @@
       <x:c r="H10" s="2"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="17" t="str">
+      <x:c r="A11" s="14" t="str">
         <x:v>operating_profit_color</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str">
+      <x:c r="B11" s="14" t="str">
         <x:v>#08A89C</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str">
+      <x:c r="C11" s="14" t="str">
         <x:v>営業利益</x:v>
       </x:c>
       <x:c r="D11" s="2"/>
@@ -474,13 +467,13 @@
       <x:c r="H11" s="2"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="17" t="str">
+      <x:c r="A12" s="14" t="str">
         <x:v>margin_color</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str">
+      <x:c r="B12" s="14" t="str">
         <x:v>#FF8A00</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str">
+      <x:c r="C12" s="14" t="str">
         <x:v>営業利益率</x:v>
       </x:c>
       <x:c r="D12" s="2"/>
@@ -490,13 +483,13 @@
       <x:c r="H12" s="2"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="17" t="str">
+      <x:c r="A13" s="14" t="str">
         <x:v>segment_revenue_subtitle</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str">
+      <x:c r="B13" s="14" t="str">
         <x:v>セグメント別 売上高の推移（円ベース）</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="14" t="str"/>
       <x:c r="D13" s="2"/>
       <x:c r="E13" s="2"/>
       <x:c r="F13" s="2"/>
@@ -504,14 +497,14 @@
       <x:c r="H13" s="2"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="17" t="str">
-        <x:v>segment_revenue_color:クラウドサービス</x:v>
-      </x:c>
-      <x:c r="B14" s="17" t="str">
+      <x:c r="A14" s="14" t="str">
+        <x:v>segment_revenue_color:クラウド</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
         <x:v>#1675F8</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str">
-        <x:v>列名と一致</x:v>
+      <x:c r="C14" s="14" t="str">
+        <x:v>セグメント名と一致</x:v>
       </x:c>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2"/>
@@ -520,13 +513,13 @@
       <x:c r="H14" s="2"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="17" t="str">
-        <x:v>segment_revenue_color:プロフェッショナルサービス</x:v>
-      </x:c>
-      <x:c r="B15" s="17" t="str">
+      <x:c r="A15" s="14" t="str">
+        <x:v>segment_revenue_color:サービス</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
         <x:v>#20B779</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="14" t="str"/>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2"/>
@@ -534,13 +527,13 @@
       <x:c r="H15" s="2"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="17" t="str">
-        <x:v>segment_revenue_color:ハードウェア</x:v>
-      </x:c>
-      <x:c r="B16" s="17" t="str">
-        <x:v>#FFA126</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="A16" s="14" t="str">
+        <x:v>segment_profit_subtitle</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>セグメント別 営業利益の推移（円ベース）</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str"/>
       <x:c r="D16" s="2"/>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2"/>
@@ -548,13 +541,13 @@
       <x:c r="H16" s="2"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="17" t="str">
-        <x:v>segment_profit_subtitle</x:v>
-      </x:c>
-      <x:c r="B17" s="17" t="str">
-        <x:v>セグメント別 営業利益の推移（円ベース）</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="str"/>
+      <x:c r="A17" s="14" t="str">
+        <x:v>segment_profit_color:クラウド</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>#1675F8</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str"/>
       <x:c r="D17" s="2"/>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2"/>
@@ -562,15 +555,13 @@
       <x:c r="H17" s="2"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="17" t="str">
-        <x:v>segment_profit_color:クラウドサービス</x:v>
-      </x:c>
-      <x:c r="B18" s="17" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="str">
-        <x:v>列名と一致</x:v>
-      </x:c>
+      <x:c r="A18" s="14" t="str">
+        <x:v>segment_profit_color:サービス</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>#20B779</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str"/>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2"/>
@@ -578,13 +569,13 @@
       <x:c r="H18" s="2"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="17" t="str">
-        <x:v>segment_profit_color:プロフェッショナルサービス</x:v>
-      </x:c>
-      <x:c r="B19" s="17" t="str">
-        <x:v>#20B779</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="str"/>
+      <x:c r="A19" s="14" t="str">
+        <x:v>orders_subtitle</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>受注高・受注残高の推移（円ベース）</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str"/>
       <x:c r="D19" s="2"/>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2"/>
@@ -592,13 +583,15 @@
       <x:c r="H19" s="2"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="17" t="str">
-        <x:v>segment_profit_color:ハードウェア</x:v>
-      </x:c>
-      <x:c r="B20" s="17" t="str">
-        <x:v>#FFA126</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="str"/>
+      <x:c r="A20" s="14" t="str">
+        <x:v>orders_color</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>#1675F8</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>受注高</x:v>
+      </x:c>
       <x:c r="D20" s="2"/>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2"/>
@@ -606,13 +599,15 @@
       <x:c r="H20" s="2"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="17" t="str">
-        <x:v>orders_subtitle</x:v>
-      </x:c>
-      <x:c r="B21" s="17" t="str">
-        <x:v>受注高・受注残高の推移（円ベース）</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="str"/>
+      <x:c r="A21" s="14" t="str">
+        <x:v>backlog_color</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>#08A89C</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>受注残高</x:v>
+      </x:c>
       <x:c r="D21" s="2"/>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2"/>
@@ -620,15 +615,13 @@
       <x:c r="H21" s="2"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="17" t="str">
-        <x:v>orders_color</x:v>
-      </x:c>
-      <x:c r="B22" s="17" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="str">
-        <x:v>受注高</x:v>
-      </x:c>
+      <x:c r="A22" s="14" t="str">
+        <x:v>arr_subtitle</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>プロダクト別 ARRの推移（円ベース）</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str"/>
       <x:c r="D22" s="2"/>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2"/>
@@ -636,15 +629,13 @@
       <x:c r="H22" s="2"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="17" t="str">
-        <x:v>backlog_color</x:v>
-      </x:c>
-      <x:c r="B23" s="17" t="str">
-        <x:v>#08A89C</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="str">
-        <x:v>受注残高</x:v>
-      </x:c>
+      <x:c r="A23" s="14" t="str">
+        <x:v>arr_color:Product A</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>#1675F8</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str"/>
       <x:c r="D23" s="2"/>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2"/>
@@ -652,13 +643,13 @@
       <x:c r="H23" s="2"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="17" t="str">
-        <x:v>arr_subtitle</x:v>
-      </x:c>
-      <x:c r="B24" s="17" t="str">
-        <x:v>プロダクト別 ARRの推移（円ベース）</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="str"/>
+      <x:c r="A24" s="14" t="str">
+        <x:v>arr_color:Product B</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>#20B779</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str"/>
       <x:c r="D24" s="2"/>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2"/>
@@ -666,15 +657,13 @@
       <x:c r="H24" s="2"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="17" t="str">
-        <x:v>arr_color:Product A</x:v>
-      </x:c>
-      <x:c r="B25" s="17" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="str">
-        <x:v>列名と一致</x:v>
-      </x:c>
+      <x:c r="A25" s="14" t="str">
+        <x:v>arr_color:Product C</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>#FFA126</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str"/>
       <x:c r="D25" s="2"/>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2"/>
@@ -682,13 +671,9 @@
       <x:c r="H25" s="2"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="17" t="str">
-        <x:v>arr_color:Product B</x:v>
-      </x:c>
-      <x:c r="B26" s="17" t="str">
-        <x:v>#20B779</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="str"/>
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
       <x:c r="D26" s="2"/>
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2"/>
@@ -696,13 +681,975 @@
       <x:c r="H26" s="2"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="17" t="str">
-        <x:v>arr_color:Product C</x:v>
-      </x:c>
-      <x:c r="B27" s="17" t="str">
-        <x:v>#FFA126</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="str"/>
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="2"/>
+      <x:c r="C28" s="2"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>ARR_四半期</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>Product A</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>Product B</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>Product C</x:v>
+      </x:c>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>2025Q1</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>2025Q2</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>2025Q3</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>2025Q4</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>2026Q4</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2"/>
+      <x:c r="B13" s="2"/>
+      <x:c r="C13" s="2"/>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="2"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2"/>
+      <x:c r="B15" s="2"/>
+      <x:c r="C15" s="2"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="2"/>
+      <x:c r="C18" s="2"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="2"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="2"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="2"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="2"/>
+      <x:c r="C28" s="2"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>ARR_年度</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>Product A</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>Product B</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>Product C</x:v>
+      </x:c>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>FY2022</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>FY2023</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>FY2024</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2"/>
+      <x:c r="B10" s="2"/>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2"/>
+      <x:c r="B12" s="2"/>
+      <x:c r="C12" s="2"/>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2"/>
+      <x:c r="B13" s="2"/>
+      <x:c r="C13" s="2"/>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="2"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2"/>
+      <x:c r="B15" s="2"/>
+      <x:c r="C15" s="2"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="2"/>
+      <x:c r="C18" s="2"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="2"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="2"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="2"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
       <x:c r="D27" s="2"/>
       <x:c r="E27" s="2"/>
       <x:c r="F27" s="2"/>
@@ -855,16 +1802,11 @@
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>会社全体</x:v>
+        <x:v>会社全体_四半期</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -876,7 +1818,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>必須列：period / revenue / operating_profit</x:v>
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -896,7 +1838,7 @@
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="22" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="10" t="str">
         <x:v>period</x:v>
       </x:c>
@@ -914,7 +1856,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>2025/3</x:v>
+        <x:v>2025Q1</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:v>250000</x:v>
@@ -930,7 +1872,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>2025/6</x:v>
+        <x:v>2025Q2</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:v>295000</x:v>
@@ -946,7 +1888,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>2025/9</x:v>
+        <x:v>2025Q3</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
         <x:v>340000</x:v>
@@ -962,7 +1904,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>2025/12</x:v>
+        <x:v>2025Q4</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
         <x:v>385000</x:v>
@@ -978,7 +1920,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>2026/3</x:v>
+        <x:v>2026Q1</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
         <x:v>430000</x:v>
@@ -994,7 +1936,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>2026/6</x:v>
+        <x:v>2026Q2</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
         <x:v>475000</x:v>
@@ -1010,7 +1952,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>2026/9</x:v>
+        <x:v>2026Q3</x:v>
       </x:c>
       <x:c r="B11" s="14" t="n">
         <x:v>520000</x:v>
@@ -1026,7 +1968,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>2026/12</x:v>
+        <x:v>2026Q4</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:v>565000</x:v>
@@ -1336,16 +2278,11 @@
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>セグメント売上高</x:v>
+        <x:v>会社全体_年度</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -1357,7 +2294,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>period以外はセグメント名。列は自由に追加・削除できます。</x:v>
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -1377,19 +2314,17 @@
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="22" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="10" t="str">
         <x:v>period</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>クラウドサービス</x:v>
+        <x:v>revenue</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>プロフェッショナルサービス</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>ハードウェア</x:v>
-      </x:c>
+        <x:v>operating_profit</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="2"/>
@@ -1397,17 +2332,15 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>2025/3</x:v>
+        <x:v>FY2022</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>110000</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="C5" s="14" t="n">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="n">
-        <x:v>30000</x:v>
-      </x:c>
+        <x:v>65000</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2"/>
@@ -1415,17 +2348,15 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>2025/6</x:v>
+        <x:v>FY2023</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>128000</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="C6" s="14" t="n">
-        <x:v>62000</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="n">
-        <x:v>38000</x:v>
-      </x:c>
+        <x:v>90000</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2"/>
@@ -1433,17 +2364,15 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>2025/9</x:v>
+        <x:v>FY2024</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>146000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="C7" s="14" t="n">
-        <x:v>74000</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="n">
-        <x:v>46000</x:v>
-      </x:c>
+        <x:v>115000</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2"/>
@@ -1451,17 +2380,15 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>2025/12</x:v>
+        <x:v>FY2025</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>164000</x:v>
+        <x:v>1350000</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>86000</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="n">
-        <x:v>54000</x:v>
-      </x:c>
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
@@ -1469,71 +2396,45 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>2026/3</x:v>
+        <x:v>FY2026</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>182000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
-        <x:v>98000</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="n">
-        <x:v>62000</x:v>
-      </x:c>
+        <x:v>165000</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>2026/6</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="n">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="n">
-        <x:v>110000</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="n">
-        <x:v>70000</x:v>
-      </x:c>
+      <x:c r="A10" s="2"/>
+      <x:c r="B10" s="2"/>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="2"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14" t="str">
-        <x:v>2026/9</x:v>
-      </x:c>
-      <x:c r="B11" s="14" t="n">
-        <x:v>218000</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="n">
-        <x:v>122000</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="n">
-        <x:v>78000</x:v>
-      </x:c>
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="14" t="str">
-        <x:v>2026/12</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="n">
-        <x:v>236000</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="n">
-        <x:v>134000</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="n">
-        <x:v>86000</x:v>
-      </x:c>
+      <x:c r="A12" s="2"/>
+      <x:c r="B12" s="2"/>
+      <x:c r="C12" s="2"/>
+      <x:c r="D12" s="2"/>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
@@ -1835,16 +2736,11 @@
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>セグメント利益</x:v>
+        <x:v>セグメント売上高_四半期</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -1856,7 +2752,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>period以外はセグメント名。</x:v>
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -1876,19 +2772,17 @@
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="22" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="10" t="str">
         <x:v>period</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>クラウドサービス</x:v>
+        <x:v>クラウド</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>プロフェッショナルサービス</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>ハードウェア</x:v>
-      </x:c>
+        <x:v>サービス</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="2"/>
@@ -1896,17 +2790,15 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>2025/3</x:v>
+        <x:v>2025Q1</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>12000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="C5" s="14" t="n">
-        <x:v>7000</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="n">
-        <x:v>5000</x:v>
-      </x:c>
+        <x:v>70000</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2"/>
@@ -1914,17 +2806,15 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>2025/6</x:v>
+        <x:v>2025Q2</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>15500</x:v>
+        <x:v>142000</x:v>
       </x:c>
       <x:c r="C6" s="14" t="n">
-        <x:v>9600</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="n">
-        <x:v>7200</x:v>
-      </x:c>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2"/>
@@ -1932,17 +2822,15 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>2025/9</x:v>
+        <x:v>2025Q3</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>19000</x:v>
+        <x:v>164000</x:v>
       </x:c>
       <x:c r="C7" s="14" t="n">
-        <x:v>12200</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="n">
-        <x:v>9400</x:v>
-      </x:c>
+        <x:v>94000</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2"/>
@@ -1950,17 +2838,15 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>2025/12</x:v>
+        <x:v>2025Q4</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>22500</x:v>
+        <x:v>186000</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>14800</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="n">
-        <x:v>11600</x:v>
-      </x:c>
+        <x:v>106000</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
@@ -1968,17 +2854,15 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>2026/3</x:v>
+        <x:v>2026Q1</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>26000</x:v>
+        <x:v>208000</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
-        <x:v>17400</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="n">
-        <x:v>13800</x:v>
-      </x:c>
+        <x:v>118000</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
@@ -1986,17 +2870,15 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>2026/6</x:v>
+        <x:v>2026Q2</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
-        <x:v>29500</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="C10" s="14" t="n">
-        <x:v>20000</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="n">
-        <x:v>16000</x:v>
-      </x:c>
+        <x:v>130000</x:v>
+      </x:c>
+      <x:c r="D10" s="2"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
@@ -2004,17 +2886,15 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>2026/9</x:v>
+        <x:v>2026Q3</x:v>
       </x:c>
       <x:c r="B11" s="14" t="n">
-        <x:v>33000</x:v>
+        <x:v>252000</x:v>
       </x:c>
       <x:c r="C11" s="14" t="n">
-        <x:v>22600</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="n">
-        <x:v>18200</x:v>
-      </x:c>
+        <x:v>142000</x:v>
+      </x:c>
+      <x:c r="D11" s="2"/>
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
@@ -2022,17 +2902,15 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>2026/12</x:v>
+        <x:v>2026Q4</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:v>36500</x:v>
+        <x:v>274000</x:v>
       </x:c>
       <x:c r="C12" s="14" t="n">
-        <x:v>25200</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="n">
-        <x:v>20400</x:v>
-      </x:c>
+        <x:v>154000</x:v>
+      </x:c>
+      <x:c r="D12" s="2"/>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
@@ -2334,16 +3212,11 @@
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>受注</x:v>
+        <x:v>セグメント売上高_年度</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -2355,7 +3228,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>必須列：period / orders / backlog</x:v>
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -2375,15 +3248,15 @@
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="22" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="10" t="str">
         <x:v>period</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>orders</x:v>
+        <x:v>クラウド</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>backlog</x:v>
+        <x:v>サービス</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -2393,13 +3266,13 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>2025/3</x:v>
+        <x:v>FY2022</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>220000</x:v>
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="C5" s="14" t="n">
-        <x:v>310000</x:v>
+        <x:v>240000</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -2409,13 +3282,13 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>2025/6</x:v>
+        <x:v>FY2023</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>285000</x:v>
+        <x:v>490000</x:v>
       </x:c>
       <x:c r="C6" s="14" t="n">
-        <x:v>400000</x:v>
+        <x:v>290000</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -2425,13 +3298,13 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>2025/9</x:v>
+        <x:v>FY2024</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>350000</x:v>
+        <x:v>580000</x:v>
       </x:c>
       <x:c r="C7" s="14" t="n">
-        <x:v>490000</x:v>
+        <x:v>340000</x:v>
       </x:c>
       <x:c r="D7" s="2"/>
       <x:c r="E7" s="2"/>
@@ -2441,13 +3314,13 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>2025/12</x:v>
+        <x:v>FY2025</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>415000</x:v>
+        <x:v>670000</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>580000</x:v>
+        <x:v>390000</x:v>
       </x:c>
       <x:c r="D8" s="2"/>
       <x:c r="E8" s="2"/>
@@ -2457,13 +3330,13 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>2026/3</x:v>
+        <x:v>FY2026</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>480000</x:v>
+        <x:v>760000</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
-        <x:v>670000</x:v>
+        <x:v>440000</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
@@ -2472,15 +3345,9 @@
       <x:c r="H9" s="2"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>2026/6</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="n">
-        <x:v>545000</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="n">
-        <x:v>760000</x:v>
-      </x:c>
+      <x:c r="A10" s="2"/>
+      <x:c r="B10" s="2"/>
+      <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
@@ -2488,15 +3355,9 @@
       <x:c r="H10" s="2"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14" t="str">
-        <x:v>2026/9</x:v>
-      </x:c>
-      <x:c r="B11" s="14" t="n">
-        <x:v>610000</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="n">
-        <x:v>850000</x:v>
-      </x:c>
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
       <x:c r="D11" s="2"/>
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
@@ -2504,15 +3365,9 @@
       <x:c r="H11" s="2"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="14" t="str">
-        <x:v>2026/12</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="n">
-        <x:v>675000</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="n">
-        <x:v>940000</x:v>
-      </x:c>
+      <x:c r="A12" s="2"/>
+      <x:c r="B12" s="2"/>
+      <x:c r="C12" s="2"/>
       <x:c r="D12" s="2"/>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
@@ -2815,16 +3670,11 @@
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>ARR</x:v>
+        <x:v>セグメント利益_四半期</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -2836,7 +3686,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>period以外はプロダクト名。複数プロダクトは積み上げ表示。</x:v>
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -2856,19 +3706,17 @@
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="22" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="10" t="str">
         <x:v>period</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Product A</x:v>
+        <x:v>クラウド</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>Product B</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>Product C</x:v>
-      </x:c>
+        <x:v>サービス</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="2"/>
@@ -2876,17 +3724,15 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>2025/3</x:v>
+        <x:v>2025Q1</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>35</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="C5" s="14" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="n">
-        <x:v>8</x:v>
-      </x:c>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2"/>
@@ -2894,17 +3740,15 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>2025/6</x:v>
+        <x:v>2025Q2</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>53</x:v>
+        <x:v>18500</x:v>
       </x:c>
       <x:c r="C6" s="14" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="n">
-        <x:v>17</x:v>
-      </x:c>
+        <x:v>8800</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2"/>
@@ -2912,17 +3756,15 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>2025/9</x:v>
+        <x:v>2025Q3</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>71</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="C7" s="14" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="n">
-        <x:v>26</x:v>
-      </x:c>
+        <x:v>10600</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2"/>
@@ -2930,17 +3772,15 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>2025/12</x:v>
+        <x:v>2025Q4</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>89</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="n">
-        <x:v>35</x:v>
-      </x:c>
+        <x:v>12400</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
@@ -2948,17 +3788,15 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>2026/3</x:v>
+        <x:v>2026Q1</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>107</x:v>
+        <x:v>29000</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="n">
-        <x:v>44</x:v>
-      </x:c>
+        <x:v>14200</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
@@ -2966,17 +3804,15 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>2026/6</x:v>
+        <x:v>2026Q2</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
-        <x:v>125</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="C10" s="14" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="n">
-        <x:v>53</x:v>
-      </x:c>
+        <x:v>16000</x:v>
+      </x:c>
+      <x:c r="D10" s="2"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
@@ -2984,17 +3820,15 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>2026/9</x:v>
+        <x:v>2026Q3</x:v>
       </x:c>
       <x:c r="B11" s="14" t="n">
-        <x:v>143</x:v>
+        <x:v>36000</x:v>
       </x:c>
       <x:c r="C11" s="14" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="n">
-        <x:v>62</x:v>
-      </x:c>
+        <x:v>17800</x:v>
+      </x:c>
+      <x:c r="D11" s="2"/>
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
@@ -3002,17 +3836,15 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>2026/12</x:v>
+        <x:v>2026Q4</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:v>161</x:v>
+        <x:v>39500</x:v>
       </x:c>
       <x:c r="C12" s="14" t="n">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="n">
-        <x:v>71</x:v>
-      </x:c>
+        <x:v>19600</x:v>
+      </x:c>
+      <x:c r="D12" s="2"/>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
@@ -3305,4 +4137,1396 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>セグメント利益_年度</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>クラウド</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>サービス</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>FY2022</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>FY2023</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>65000</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>FY2024</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>41000</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>95000</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>49000</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>110000</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>57000</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2"/>
+      <x:c r="B10" s="2"/>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2"/>
+      <x:c r="B12" s="2"/>
+      <x:c r="C12" s="2"/>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2"/>
+      <x:c r="B13" s="2"/>
+      <x:c r="C13" s="2"/>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="2"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2"/>
+      <x:c r="B15" s="2"/>
+      <x:c r="C15" s="2"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="2"/>
+      <x:c r="C18" s="2"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="2"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="2"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="2"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="2"/>
+      <x:c r="C28" s="2"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>受注_四半期</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>orders</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>backlog</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>2025Q1</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>220000</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>310000</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>2025Q2</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>280000</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>395000</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>2025Q3</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>340000</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>480000</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>2025Q4</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>565000</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>460000</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>650000</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="n">
+        <x:v>520000</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="n">
+        <x:v>735000</x:v>
+      </x:c>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="n">
+        <x:v>580000</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="n">
+        <x:v>820000</x:v>
+      </x:c>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>2026Q4</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="n">
+        <x:v>640000</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="n">
+        <x:v>905000</x:v>
+      </x:c>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2"/>
+      <x:c r="B13" s="2"/>
+      <x:c r="C13" s="2"/>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="2"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2"/>
+      <x:c r="B15" s="2"/>
+      <x:c r="C15" s="2"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="2"/>
+      <x:c r="C18" s="2"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="2"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="2"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="2"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="2"/>
+      <x:c r="C28" s="2"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>受注_年度</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>orders</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>backlog</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>FY2022</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>750000</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>FY2023</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>930000</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>1260000</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>FY2024</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>1110000</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>1520000</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>1290000</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>1780000</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>1470000</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>2040000</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2"/>
+      <x:c r="B10" s="2"/>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2"/>
+      <x:c r="B12" s="2"/>
+      <x:c r="C12" s="2"/>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2"/>
+      <x:c r="B13" s="2"/>
+      <x:c r="C13" s="2"/>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="2"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2"/>
+      <x:c r="B15" s="2"/>
+      <x:c r="C15" s="2"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="2"/>
+      <x:c r="C18" s="2"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="2"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="2"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="2"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="2"/>
+      <x:c r="C28" s="2"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rcfb97edeee5d4f27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R1e989b81a9fc4baf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R4f8cbb295fa84980"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R461e0abb93d34c95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rb2d426add6664c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R8e4e205473914d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R5278f08d0c354494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R086acb5cfe854172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="Rde78ec81d6214568"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rfb106c1610434092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R499619424c034ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R9b4b5d7ff55e423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R64a4dbf4bca44890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R52e26bb35c8841b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R1f04aa45dd3a4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rbbc22b66e0124ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rf031eccc5f5943ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R479231a0464543e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="Re23e4059819a4d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R9d1bda67da0040cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rafce32231cb3483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Re7cef102c2214ea6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,8 +50,14 @@
       <x:color rgb="FF17325C"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17325C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -68,6 +74,16 @@
         <x:fgColor rgb="FF17325C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17325C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE8F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -76,7 +92,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -97,6 +113,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -302,6 +326,9 @@
     <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -339,19 +366,25 @@
       <x:c r="H3" s="2"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="10" t="str">
+      <x:c r="A4" s="17" t="str">
         <x:v>setting</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="str">
+      <x:c r="B4" s="17" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="C4" s="10" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>説明</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
-      <x:c r="E4" s="2"/>
-      <x:c r="F4" s="2"/>
-      <x:c r="G4" s="2"/>
+      <x:c r="E4" s="17" t="str">
+        <x:v>種類</x:v>
+      </x:c>
+      <x:c r="F4" s="17" t="str">
+        <x:v>項目名</x:v>
+      </x:c>
+      <x:c r="G4" s="17" t="str">
+        <x:v>カラー</x:v>
+      </x:c>
       <x:c r="H4" s="2"/>
     </x:row>
     <x:row r="5">
@@ -365,9 +398,15 @@
         <x:v>企業名</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
-      <x:c r="E5" s="2"/>
-      <x:c r="F5" s="2"/>
-      <x:c r="G5" s="2"/>
+      <x:c r="E5" s="2" t="str">
+        <x:v>セグメント</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="str">
+        <x:v>クラウド</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="str">
+        <x:v>#1675F8</x:v>
+      </x:c>
       <x:c r="H5" s="2"/>
     </x:row>
     <x:row r="6">
@@ -381,9 +420,15 @@
         <x:v>共通注意書き</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
-      <x:c r="E6" s="2"/>
-      <x:c r="F6" s="2"/>
-      <x:c r="G6" s="2"/>
+      <x:c r="E6" s="2" t="str">
+        <x:v>セグメント</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="str">
+        <x:v>サービス</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="str">
+        <x:v>#20B779</x:v>
+      </x:c>
       <x:c r="H6" s="2"/>
     </x:row>
     <x:row r="7">
@@ -397,9 +442,15 @@
         <x:v>JPY/USD/EUR/CNY/DKK/KRW/NOK/SEK/CHF/TWD/HKD</x:v>
       </x:c>
       <x:c r="D7" s="2"/>
-      <x:c r="E7" s="2"/>
-      <x:c r="F7" s="2"/>
-      <x:c r="G7" s="2"/>
+      <x:c r="E7" s="2" t="str">
+        <x:v>ARR</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="str">
+        <x:v>Product A</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="str">
+        <x:v>#1675F8</x:v>
+      </x:c>
       <x:c r="H7" s="2"/>
     </x:row>
     <x:row r="8">
@@ -413,9 +464,15 @@
         <x:v>表示単位</x:v>
       </x:c>
       <x:c r="D8" s="2"/>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="2"/>
-      <x:c r="G8" s="2"/>
+      <x:c r="E8" s="2" t="str">
+        <x:v>ARR</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="str">
+        <x:v>Product B</x:v>
+      </x:c>
+      <x:c r="G8" s="2" t="str">
+        <x:v>#20B779</x:v>
+      </x:c>
       <x:c r="H8" s="2"/>
     </x:row>
     <x:row r="9">
@@ -429,9 +486,15 @@
         <x:v>会社全体</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
-      <x:c r="G9" s="2"/>
+      <x:c r="E9" s="2" t="str">
+        <x:v>ARR</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="str">
+        <x:v>Product C</x:v>
+      </x:c>
+      <x:c r="G9" s="2" t="str">
+        <x:v>#FFA126</x:v>
+      </x:c>
       <x:c r="H9" s="2"/>
     </x:row>
     <x:row r="10">
@@ -461,9 +524,11 @@
         <x:v>営業利益</x:v>
       </x:c>
       <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="2"/>
+      <x:c r="E11" s="21" t="str">
+        <x:v>使い方</x:v>
+      </x:c>
+      <x:c r="F11" s="21" t="str"/>
+      <x:c r="G11" s="21" t="str"/>
       <x:c r="H11" s="2"/>
     </x:row>
     <x:row r="12">
@@ -477,9 +542,15 @@
         <x:v>営業利益率</x:v>
       </x:c>
       <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
+      <x:c r="E12" s="2" t="str">
+        <x:v>セグメントを増やす</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="str">
+        <x:v>E:Gに1行追加</x:v>
+      </x:c>
+      <x:c r="G12" s="2" t="str">
+        <x:v>売上高・利益の両方で同じ色を使用</x:v>
+      </x:c>
       <x:c r="H12" s="2"/>
     </x:row>
     <x:row r="13">
@@ -491,21 +562,25 @@
       </x:c>
       <x:c r="C13" s="14" t="str"/>
       <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
+      <x:c r="E13" s="2" t="str">
+        <x:v>ARRを増やす</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="str">
+        <x:v>E:Gに1行追加</x:v>
+      </x:c>
+      <x:c r="G13" s="2" t="str">
+        <x:v>種類をARRにする</x:v>
+      </x:c>
       <x:c r="H13" s="2"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>segment_revenue_color:クラウド</x:v>
+        <x:v>segment_profit_subtitle</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="str">
-        <x:v>セグメント名と一致</x:v>
-      </x:c>
+        <x:v>セグメント別 営業利益の推移（円ベース）</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str"/>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2"/>
@@ -514,10 +589,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>segment_revenue_color:サービス</x:v>
+        <x:v>orders_subtitle</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>#20B779</x:v>
+        <x:v>受注高・受注残高の推移（円ベース）</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str"/>
       <x:c r="D15" s="2"/>
@@ -528,12 +603,14 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
-        <x:v>segment_profit_subtitle</x:v>
+        <x:v>orders_color</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>セグメント別 営業利益の推移（円ベース）</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="str"/>
+        <x:v>#1675F8</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>受注高</x:v>
+      </x:c>
       <x:c r="D16" s="2"/>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2"/>
@@ -542,12 +619,14 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
-        <x:v>segment_profit_color:クラウド</x:v>
+        <x:v>backlog_color</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="str"/>
+        <x:v>#08A89C</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>受注残高</x:v>
+      </x:c>
       <x:c r="D17" s="2"/>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2"/>
@@ -556,10 +635,10 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
-        <x:v>segment_profit_color:サービス</x:v>
+        <x:v>arr_subtitle</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>#20B779</x:v>
+        <x:v>プロダクト別 ARRの推移（円ベース）</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str"/>
       <x:c r="D18" s="2"/>
@@ -569,13 +648,9 @@
       <x:c r="H18" s="2"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="14" t="str">
-        <x:v>orders_subtitle</x:v>
-      </x:c>
-      <x:c r="B19" s="14" t="str">
-        <x:v>受注高・受注残高の推移（円ベース）</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="str"/>
+      <x:c r="A19" s="14"/>
+      <x:c r="B19" s="14"/>
+      <x:c r="C19" s="14"/>
       <x:c r="D19" s="2"/>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2"/>
@@ -583,15 +658,9 @@
       <x:c r="H19" s="2"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="14" t="str">
-        <x:v>orders_color</x:v>
-      </x:c>
-      <x:c r="B20" s="14" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="str">
-        <x:v>受注高</x:v>
-      </x:c>
+      <x:c r="A20" s="14"/>
+      <x:c r="B20" s="14"/>
+      <x:c r="C20" s="14"/>
       <x:c r="D20" s="2"/>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2"/>
@@ -599,15 +668,9 @@
       <x:c r="H20" s="2"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="14" t="str">
-        <x:v>backlog_color</x:v>
-      </x:c>
-      <x:c r="B21" s="14" t="str">
-        <x:v>#08A89C</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="str">
-        <x:v>受注残高</x:v>
-      </x:c>
+      <x:c r="A21" s="14"/>
+      <x:c r="B21" s="14"/>
+      <x:c r="C21" s="14"/>
       <x:c r="D21" s="2"/>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2"/>
@@ -615,13 +678,9 @@
       <x:c r="H21" s="2"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="14" t="str">
-        <x:v>arr_subtitle</x:v>
-      </x:c>
-      <x:c r="B22" s="14" t="str">
-        <x:v>プロダクト別 ARRの推移（円ベース）</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="str"/>
+      <x:c r="A22" s="14"/>
+      <x:c r="B22" s="14"/>
+      <x:c r="C22" s="14"/>
       <x:c r="D22" s="2"/>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2"/>
@@ -629,13 +688,9 @@
       <x:c r="H22" s="2"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="14" t="str">
-        <x:v>arr_color:Product A</x:v>
-      </x:c>
-      <x:c r="B23" s="14" t="str">
-        <x:v>#1675F8</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="str"/>
+      <x:c r="A23" s="14"/>
+      <x:c r="B23" s="14"/>
+      <x:c r="C23" s="14"/>
       <x:c r="D23" s="2"/>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2"/>
@@ -643,13 +698,9 @@
       <x:c r="H23" s="2"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="14" t="str">
-        <x:v>arr_color:Product B</x:v>
-      </x:c>
-      <x:c r="B24" s="14" t="str">
-        <x:v>#20B779</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="str"/>
+      <x:c r="A24" s="14"/>
+      <x:c r="B24" s="14"/>
+      <x:c r="C24" s="14"/>
       <x:c r="D24" s="2"/>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2"/>
@@ -657,13 +708,9 @@
       <x:c r="H24" s="2"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="14" t="str">
-        <x:v>arr_color:Product C</x:v>
-      </x:c>
-      <x:c r="B25" s="14" t="str">
-        <x:v>#FFA126</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="str"/>
+      <x:c r="A25" s="14"/>
+      <x:c r="B25" s="14"/>
+      <x:c r="C25" s="14"/>
       <x:c r="D25" s="2"/>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2"/>

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R9b4b5d7ff55e423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R64a4dbf4bca44890"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R52e26bb35c8841b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R1f04aa45dd3a4352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rbbc22b66e0124ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rf031eccc5f5943ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R479231a0464543e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="Re23e4059819a4d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R9d1bda67da0040cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rafce32231cb3483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Re7cef102c2214ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R1a219b860e5c41f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R1fee2a9ccd6c4ee6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R1af53ddff04840c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R23fc74b7e43d4ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Ra8a67da167b24f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R7dc15b8a8ad84d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R2bc25862ad284d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="Re18075796ecd41de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="Re982e1e677d04b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Re95cccc7f5e748e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Rb415eb81a6304b09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -458,10 +458,10 @@
         <x:v>display_unit</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>億円</x:v>
+        <x:v>億（現地通貨）</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>表示単位</x:v>
+        <x:v>初期値：入力通貨の「億」単位（例：JPY=億円、USD=億ドル、KRW=億ウォン）</x:v>
       </x:c>
       <x:c r="D8" s="2"/>
       <x:c r="E8" s="2" t="str">
@@ -479,11 +479,9 @@
       <x:c r="A9" s="14" t="str">
         <x:v>company_subtitle</x:v>
       </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>売上高・営業利益・営業利益率の推移（円ベース）</x:v>
-      </x:c>
+      <x:c r="B9" s="14" t="str"/>
       <x:c r="C9" s="14" t="str">
-        <x:v>会社全体</x:v>
+        <x:v>空欄時：四半期は「四半期業績」、年度は「年度業績」</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
       <x:c r="E9" s="2" t="str">

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R1a219b860e5c41f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R1fee2a9ccd6c4ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R1af53ddff04840c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R23fc74b7e43d4ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Ra8a67da167b24f17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R7dc15b8a8ad84d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R2bc25862ad284d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="Re18075796ecd41de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="Re982e1e677d04b03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Re95cccc7f5e748e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Rb415eb81a6304b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R2628d36135424a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R26d90cbf6fb64fc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="Rfe0db5b6be664aab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="Ra92e8deb399c4187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R924ec80e822c4b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R8d29eb33af49423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R65a7d6a1e83048e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R96b4f44205314259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R6d7c5720e8e54429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R36267c4155614bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Rb64411ce08534fcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -121,6 +121,15 @@
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -326,9 +335,10 @@
     <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -376,16 +386,18 @@
         <x:v>説明</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
-      <x:c r="E4" s="17" t="str">
+      <x:c r="E4" s="22" t="str">
         <x:v>種類</x:v>
       </x:c>
-      <x:c r="F4" s="17" t="str">
+      <x:c r="F4" s="22" t="str">
         <x:v>項目名</x:v>
       </x:c>
-      <x:c r="G4" s="17" t="str">
+      <x:c r="G4" s="22" t="str">
+        <x:v>表示名</x:v>
+      </x:c>
+      <x:c r="H4" s="23" t="str">
         <x:v>カラー</x:v>
       </x:c>
-      <x:c r="H4" s="2"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -398,16 +410,18 @@
         <x:v>企業名</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
-      <x:c r="E5" s="2" t="str">
+      <x:c r="E5" s="23" t="str">
         <x:v>セグメント</x:v>
       </x:c>
-      <x:c r="F5" s="2" t="str">
+      <x:c r="F5" s="23" t="str">
         <x:v>クラウド</x:v>
       </x:c>
-      <x:c r="G5" s="2" t="str">
+      <x:c r="G5" s="23" t="str">
+        <x:v>クラウド</x:v>
+      </x:c>
+      <x:c r="H5" s="23" t="str">
         <x:v>#1675F8</x:v>
       </x:c>
-      <x:c r="H5" s="2"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
@@ -420,16 +434,18 @@
         <x:v>共通注意書き</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
-      <x:c r="E6" s="2" t="str">
+      <x:c r="E6" s="23" t="str">
         <x:v>セグメント</x:v>
       </x:c>
-      <x:c r="F6" s="2" t="str">
+      <x:c r="F6" s="23" t="str">
         <x:v>サービス</x:v>
       </x:c>
-      <x:c r="G6" s="2" t="str">
+      <x:c r="G6" s="23" t="str">
+        <x:v>サービス</x:v>
+      </x:c>
+      <x:c r="H6" s="23" t="str">
         <x:v>#20B779</x:v>
       </x:c>
-      <x:c r="H6" s="2"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
@@ -442,16 +458,18 @@
         <x:v>JPY/USD/EUR/CNY/DKK/KRW/NOK/SEK/CHF/TWD/HKD</x:v>
       </x:c>
       <x:c r="D7" s="2"/>
-      <x:c r="E7" s="2" t="str">
+      <x:c r="E7" s="23" t="str">
         <x:v>ARR</x:v>
       </x:c>
-      <x:c r="F7" s="2" t="str">
+      <x:c r="F7" s="23" t="str">
         <x:v>Product A</x:v>
       </x:c>
-      <x:c r="G7" s="2" t="str">
+      <x:c r="G7" s="23" t="str">
+        <x:v>Product A</x:v>
+      </x:c>
+      <x:c r="H7" s="23" t="str">
         <x:v>#1675F8</x:v>
       </x:c>
-      <x:c r="H7" s="2"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
@@ -464,16 +482,18 @@
         <x:v>初期値：入力通貨の「億」単位（例：JPY=億円、USD=億ドル、KRW=億ウォン）</x:v>
       </x:c>
       <x:c r="D8" s="2"/>
-      <x:c r="E8" s="2" t="str">
+      <x:c r="E8" s="23" t="str">
         <x:v>ARR</x:v>
       </x:c>
-      <x:c r="F8" s="2" t="str">
+      <x:c r="F8" s="23" t="str">
         <x:v>Product B</x:v>
       </x:c>
-      <x:c r="G8" s="2" t="str">
+      <x:c r="G8" s="23" t="str">
+        <x:v>Product B</x:v>
+      </x:c>
+      <x:c r="H8" s="23" t="str">
         <x:v>#20B779</x:v>
       </x:c>
-      <x:c r="H8" s="2"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -484,16 +504,18 @@
         <x:v>空欄時：四半期は「四半期業績」、年度は「年度業績」</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2" t="str">
+      <x:c r="E9" s="23" t="str">
         <x:v>ARR</x:v>
       </x:c>
-      <x:c r="F9" s="2" t="str">
+      <x:c r="F9" s="23" t="str">
         <x:v>Product C</x:v>
       </x:c>
-      <x:c r="G9" s="2" t="str">
+      <x:c r="G9" s="23" t="str">
+        <x:v>Product C</x:v>
+      </x:c>
+      <x:c r="H9" s="23" t="str">
         <x:v>#FFA126</x:v>
       </x:c>
-      <x:c r="H9" s="2"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
@@ -506,10 +528,10 @@
         <x:v>売上高</x:v>
       </x:c>
       <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2"/>
+      <x:c r="E10" s="23"/>
+      <x:c r="F10" s="23"/>
+      <x:c r="G10" s="23"/>
+      <x:c r="H10" s="23"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
@@ -522,12 +544,12 @@
         <x:v>営業利益</x:v>
       </x:c>
       <x:c r="D11" s="2"/>
-      <x:c r="E11" s="21" t="str">
+      <x:c r="E11" s="24" t="str">
         <x:v>使い方</x:v>
       </x:c>
-      <x:c r="F11" s="21" t="str"/>
-      <x:c r="G11" s="21" t="str"/>
-      <x:c r="H11" s="2"/>
+      <x:c r="F11" s="24"/>
+      <x:c r="G11" s="24"/>
+      <x:c r="H11" s="23"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -540,16 +562,18 @@
         <x:v>営業利益率</x:v>
       </x:c>
       <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2" t="str">
+      <x:c r="E12" s="23" t="str">
         <x:v>セグメントを増やす</x:v>
       </x:c>
-      <x:c r="F12" s="2" t="str">
-        <x:v>E:Gに1行追加</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="str">
-        <x:v>売上高・利益の両方で同じ色を使用</x:v>
-      </x:c>
-      <x:c r="H12" s="2"/>
+      <x:c r="F12" s="23" t="str">
+        <x:v>E:Hに1行追加</x:v>
+      </x:c>
+      <x:c r="G12" s="23" t="str">
+        <x:v>画像上の名称をG列で変更</x:v>
+      </x:c>
+      <x:c r="H12" s="23" t="str">
+        <x:v>売上高・利益で共通</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
@@ -560,16 +584,18 @@
       </x:c>
       <x:c r="C13" s="14" t="str"/>
       <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2" t="str">
+      <x:c r="E13" s="23" t="str">
         <x:v>ARRを増やす</x:v>
       </x:c>
-      <x:c r="F13" s="2" t="str">
-        <x:v>E:Gに1行追加</x:v>
-      </x:c>
-      <x:c r="G13" s="2" t="str">
+      <x:c r="F13" s="23" t="str">
+        <x:v>E:Hに1行追加</x:v>
+      </x:c>
+      <x:c r="G13" s="23" t="str">
+        <x:v>画像上の名称をG列で変更</x:v>
+      </x:c>
+      <x:c r="H13" s="23" t="str">
         <x:v>種類をARRにする</x:v>
       </x:c>
-      <x:c r="H13" s="2"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,19 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R869e4d66b16c4038"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R74e4e9bcd11e46de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R1b16b9c79834475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R329f99849f384911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R93da1f6575eb410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rcce0f6329c2a42e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="Rd1396a21aa694a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R8c115dbef03444d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="Rd11bf677125f40c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R83adbbd976bf4205"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R3356b4ca5cfb4e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R119fd612d10d4036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="Rc38c1381fcd04286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R088e1e2ced2e40d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R011e177d16bc4268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R819457463948422e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R911607c5ae054445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R9e04efa2c67945f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R686119c4ceb54864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="Re87517d5b8394c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R4199fb39d2314ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="Rd1e1d093e6be454f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rdab01fe5f9ab45a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R588c65162b864916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R67f687c8a8c34c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="Rd95452d6e56d4afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="R5c6a7826adfd4b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="R511ea92c82b74dd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R8b932157298e4fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R1ef632fe66124734"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -697,10 +701,18 @@
         </x:is>
       </x:c>
       <x:c r="D10" s="2" t="n"/>
-      <x:c r="E10" s="23" t="n"/>
-      <x:c r="F10" s="23" t="n"/>
-      <x:c r="G10" s="23" t="n"/>
-      <x:c r="H10" s="23" t="n"/>
+      <x:c r="E10" s="23" t="str">
+        <x:v>品目別受注高</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="str">
+        <x:v>#1675F8</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="inlineStr">
@@ -719,14 +731,18 @@
         </x:is>
       </x:c>
       <x:c r="D11" s="2" t="n"/>
-      <x:c r="E11" s="24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">使い方</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="24" t="n"/>
-      <x:c r="G11" s="24" t="n"/>
-      <x:c r="H11" s="23" t="n"/>
+      <x:c r="E11" s="24" t="str">
+        <x:v>品目別受注高</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="H11" s="23" t="str">
+        <x:v>#20B779</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="inlineStr">
@@ -745,25 +761,17 @@
         </x:is>
       </x:c>
       <x:c r="D12" s="2" t="n"/>
-      <x:c r="E12" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">セグメント区分2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">種類を「セグメント2」にする</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">表示名を自由に設定</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">売上高2で使用</x:t>
-        </x:is>
+      <x:c r="E12" s="23" t="str">
+        <x:v>品目別受注高</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="G12" s="23" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="H12" s="23" t="str">
+        <x:v>#FFA126</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -779,25 +787,17 @@
       </x:c>
       <x:c r="C13" s="14" t="str"/>
       <x:c r="D13" s="2" t="n"/>
-      <x:c r="E13" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ARRを増やす</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">E:Hに1行追加</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">画像上の名称をG列で変更</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">種類をARRにする</x:t>
-        </x:is>
+      <x:c r="E13" s="23" t="str">
+        <x:v>品目別受注残高</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="G13" s="23" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="H13" s="23" t="str">
+        <x:v>#7C3AED</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -816,6 +816,18 @@
           <x:t xml:space="preserve">セグメント区分2の売上高サブタイトル</x:t>
         </x:is>
       </x:c>
+      <x:c r="E14" t="str">
+        <x:v>品目別受注残高</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>#EC4899</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="inlineStr">
@@ -830,10 +842,18 @@
       </x:c>
       <x:c r="C15" s="14" t="str"/>
       <x:c r="D15" s="2" t="n"/>
-      <x:c r="E15" s="2" t="n"/>
-      <x:c r="F15" s="2" t="n"/>
-      <x:c r="G15" s="2" t="n"/>
-      <x:c r="H15" s="2" t="n"/>
+      <x:c r="E15" s="2" t="str">
+        <x:v>品目別受注残高</x:v>
+      </x:c>
+      <x:c r="F15" s="2" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="G15" s="2" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="H15" s="2" t="str">
+        <x:v>#64748B</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="inlineStr">
@@ -848,10 +868,10 @@
       </x:c>
       <x:c r="C16" s="14" t="str"/>
       <x:c r="D16" s="2" t="n"/>
-      <x:c r="E16" s="2" t="n"/>
-      <x:c r="F16" s="2" t="n"/>
-      <x:c r="G16" s="2" t="n"/>
-      <x:c r="H16" s="2" t="n"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="inlineStr">
@@ -870,10 +890,12 @@
         </x:is>
       </x:c>
       <x:c r="D17" s="2" t="n"/>
-      <x:c r="E17" s="2" t="n"/>
-      <x:c r="F17" s="2" t="n"/>
-      <x:c r="G17" s="2" t="n"/>
-      <x:c r="H17" s="2" t="n"/>
+      <x:c r="E17" s="2" t="str">
+        <x:v>使い方</x:v>
+      </x:c>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="inlineStr">
@@ -892,10 +914,18 @@
         </x:is>
       </x:c>
       <x:c r="D18" s="2" t="n"/>
-      <x:c r="E18" s="2" t="n"/>
-      <x:c r="F18" s="2" t="n"/>
-      <x:c r="G18" s="2" t="n"/>
-      <x:c r="H18" s="2" t="n"/>
+      <x:c r="E18" s="2" t="str">
+        <x:v>セグメント区分2</x:v>
+      </x:c>
+      <x:c r="F18" s="2" t="str">
+        <x:v>種類を「セグメント2」にする</x:v>
+      </x:c>
+      <x:c r="G18" s="2" t="str">
+        <x:v>表示名を自由に設定</x:v>
+      </x:c>
+      <x:c r="H18" s="2" t="str">
+        <x:v>売上高2で使用</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="inlineStr">
@@ -910,10 +940,18 @@
       </x:c>
       <x:c r="C19" s="14" t="str"/>
       <x:c r="D19" s="2" t="n"/>
-      <x:c r="E19" s="2" t="n"/>
-      <x:c r="F19" s="2" t="n"/>
-      <x:c r="G19" s="2" t="n"/>
-      <x:c r="H19" s="2" t="n"/>
+      <x:c r="E19" s="2" t="str">
+        <x:v>ARRを増やす</x:v>
+      </x:c>
+      <x:c r="F19" s="2" t="str">
+        <x:v>E:Hに1行追加</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="str">
+        <x:v>画像上の名称をG列で変更</x:v>
+      </x:c>
+      <x:c r="H19" s="2" t="str">
+        <x:v>種類をARRにする</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
@@ -932,9 +970,15 @@
       <x:c r="H20" s="2" t="n"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="14" t="n"/>
-      <x:c r="B21" s="14" t="n"/>
-      <x:c r="C21" s="14" t="n"/>
+      <x:c r="A21" s="14" t="str">
+        <x:v>orders_by_item_subtitle</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>品目別 受注高の推移</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>品目別受注高グラフのサブタイトル</x:v>
+      </x:c>
       <x:c r="D21" s="2" t="n"/>
       <x:c r="E21" s="2" t="n"/>
       <x:c r="F21" s="2" t="n"/>
@@ -942,9 +986,15 @@
       <x:c r="H21" s="2" t="n"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="14" t="n"/>
-      <x:c r="B22" s="14" t="n"/>
-      <x:c r="C22" s="14" t="n"/>
+      <x:c r="A22" s="14" t="str">
+        <x:v>backlog_by_item_subtitle</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>品目別 受注残高の推移</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>品目別受注残高グラフのサブタイトル</x:v>
+      </x:c>
       <x:c r="D22" s="2" t="n"/>
       <x:c r="E22" s="2" t="n"/>
       <x:c r="F22" s="2" t="n"/>
@@ -3190,6 +3240,1930 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>品目別受注高_四半期</x:v>
+      </x:c>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>2025Q1</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>145000</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>2025Q2</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>152250</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>55120</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>19260</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>2025Q3</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>159500</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>58240</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>20520</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>2025Q4</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>166750</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>61360</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>21780</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>174000</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>64480</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>23040</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>181250</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>67600</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>24300</x:v>
+      </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>188500</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>70720</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>25560</x:v>
+      </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>2026Q4</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>195750</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>73840</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>26820</x:v>
+      </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>品目別受注高_年度</x:v>
+      </x:c>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>FY2022</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>145000</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>FY2023</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>152250</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>55120</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>19260</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>FY2024</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>159500</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>58240</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>20520</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>166750</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>61360</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>21780</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>174000</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>64480</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>23040</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>品目別受注残高_四半期</x:v>
+      </x:c>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>2025Q1</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>520000</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>2025Q2</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>546000</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>180200</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>48150</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>2025Q3</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>572000</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>190400</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>51300</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>2025Q4</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>598000</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>200600</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>54450</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>624000</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>210800</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>57600</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>650000</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>221000</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>60750</x:v>
+      </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>676000</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>231200</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>63900</x:v>
+      </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>2026Q4</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>702000</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>241400</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>67050</x:v>
+      </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>品目別受注残高_年度</x:v>
+      </x:c>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">四半期と年度は別シートで管理します。period以外の可変列は自由に追加・削除できます。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>period</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>半導体製造装置</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>FPD製造装置</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>その他</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>FY2022</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>520000</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>FY2023</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>546000</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>180200</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>48150</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>FY2024</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>572000</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>190400</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>51300</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>598000</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>200600</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>54450</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>624000</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>210800</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>57600</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rb178d39259dd4bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="Rcde220aa7e544fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R3dac53f9067b4ef2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="Rf3fc3ec089bd4acf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rf7e4744606a143cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R7d5f2e9d7fa74274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R7b923f57540b43f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R59fdbd12483c4add"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R1ca90f3b114c4b92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R83f4f9e69d3f4338"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R2f4c5189ab1f467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R8de68943a44b43e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="Raba1fe52053b4a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="R04e5d277e58f4497"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="R7a28e865ae1443bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="Ref3f12939de147a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="Rebb4da9882244cce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R8423b2e52b6546a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R7da2f699d99a4b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rf200654abf214f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R2b2adf6e9d65427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="Rea70d5dc384240a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R12a98f1231884dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R661e87f0a09441d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R9d960f6509914437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R766a174fa720462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R747d8cafff6e4471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R688f9038da244cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rba6d7587db3345c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Rb1eb53f0cfde480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="Rf106cebb58f04017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R9cad80e5114f435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="R9ee0e71c186f4cc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="Re4fed10b987f401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R9192faf8043a4169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R6d5b0834be754c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R4d3a5c831de24891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R53cfba2a60d84e74"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -449,9 +449,15 @@
       <x:c r="H2" s="1" t="n"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="n"/>
-      <x:c r="B3" s="2" t="n"/>
-      <x:c r="C3" s="2" t="n"/>
+      <x:c r="A3" s="2" t="str">
+        <x:v>orders_label</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>受注高</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>受注高系列の表示名。例：受注高 / cRPO / order</x:v>
+      </x:c>
       <x:c r="D3" s="2" t="n"/>
       <x:c r="E3" s="2" t="n"/>
       <x:c r="F3" s="2" t="n"/>

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rf200654abf214f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R2b2adf6e9d65427d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="Rea70d5dc384240a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R12a98f1231884dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R661e87f0a09441d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R9d960f6509914437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R766a174fa720462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R747d8cafff6e4471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R688f9038da244cae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rba6d7587db3345c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="Rb1eb53f0cfde480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="Rf106cebb58f04017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R9cad80e5114f435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="R9ee0e71c186f4cc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="Re4fed10b987f401d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R9192faf8043a4169"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R6d5b0834be754c80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R4d3a5c831de24891"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R53cfba2a60d84e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rc14e0fb4eaf245af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R397ccb10fd064ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R6a4ddcc6162b4435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="Rf9a9bfff159045fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rd85266662d73496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rc10f79b1d17e4e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R6e7afab991884d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R7aed6bce778c44f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R1cd68bb012f54a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rd082ab46471b41e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R57aadc75f6d1448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R832b19f6a17d4a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R5590ef24cd3046e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="R00afe48a534849d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="Reedc230ac99546e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R6f1a47c13caa4abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="Rc9ce16a0c28f4592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R319d6ff3012048f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R909065857ef54ea4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -449,15 +449,9 @@
       <x:c r="H2" s="1" t="n"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>orders_label</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v>受注高</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="str">
-        <x:v>受注高系列の表示名。例：受注高 / cRPO / order</x:v>
-      </x:c>
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
       <x:c r="D3" s="2" t="n"/>
       <x:c r="E3" s="2" t="n"/>
       <x:c r="F3" s="2" t="n"/>
@@ -1170,9 +1164,15 @@
       <x:c r="H26" s="2" t="n"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="2" t="n"/>
-      <x:c r="B27" s="2" t="n"/>
-      <x:c r="C27" s="2" t="n"/>
+      <x:c r="A27" s="2" t="str">
+        <x:v>orders_label</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>受注高</x:v>
+      </x:c>
+      <x:c r="C27" s="2" t="str">
+        <x:v>受注高系列の表示名。例：受注高 / cRPO / order</x:v>
+      </x:c>
       <x:c r="D27" s="2" t="n"/>
       <x:c r="E27" s="2" t="n"/>
       <x:c r="F27" s="2" t="n"/>

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rc14e0fb4eaf245af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R397ccb10fd064ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R6a4ddcc6162b4435"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="Rf9a9bfff159045fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rd85266662d73496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rc10f79b1d17e4e71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R6e7afab991884d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R7aed6bce778c44f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R1cd68bb012f54a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="Rd082ab46471b41e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R57aadc75f6d1448e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R832b19f6a17d4a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R5590ef24cd3046e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="R00afe48a534849d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="Reedc230ac99546e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R6f1a47c13caa4abf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="Rc9ce16a0c28f4592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R319d6ff3012048f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R909065857ef54ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rba848f97553d4a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R4da889646b504989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R282bf01e1f744b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R94cb7510cb204998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rf0102fce53dd4420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rffdeebf81c0e4d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R7d78813aa63c47f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R0924dfbdbd1a48f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R52ebc4a30c2949cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R04f446dece7a42fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R1de8c5e9bd084d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R795d7e3aebc943cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R0916de4cb31a463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="Ra74df5ee81a043ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="R38cd691886444dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R2aadafea42c94bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R5d162be405c247e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R680678f69bef4335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R6e5b88f90553494a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1441,7 +1441,9 @@
           <x:t xml:space="preserve">Product C</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="2" t="n"/>
+      <x:c r="E4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
       <x:c r="H4" s="2" t="n"/>
@@ -2451,7 +2453,9 @@
           <x:t xml:space="preserve">サービス</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -2953,7 +2957,9 @@
           <x:t xml:space="preserve">サービス</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -3413,6 +3419,9 @@
         <x:is>
           <x:t xml:space="preserve">その他</x:t>
         </x:is>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>guidance</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3621,6 +3630,9 @@
         <x:is>
           <x:t xml:space="preserve">その他</x:t>
         </x:is>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>guidance</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3785,6 +3797,9 @@
           <x:t xml:space="preserve">その他</x:t>
         </x:is>
       </x:c>
+      <x:c r="E4" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
@@ -3993,6 +4008,9 @@
           <x:t xml:space="preserve">その他</x:t>
         </x:is>
       </x:c>
+      <x:c r="E4" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
@@ -4145,7 +4163,9 @@
       <x:c r="B4" t="str">
         <x:v>ARR</x:v>
       </x:c>
-      <x:c r="C4"/>
+      <x:c r="C4" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="D4"/>
     </x:row>
     <x:row r="5">
@@ -4241,6 +4261,9 @@
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Product C</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>guidance</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4439,7 +4462,9 @@
           <x:t xml:space="preserve">operating_profit</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -4941,7 +4966,9 @@
           <x:t xml:space="preserve">operating_profit</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -5419,7 +5446,9 @@
           <x:t xml:space="preserve">サービス</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -5921,7 +5950,9 @@
           <x:t xml:space="preserve">サービス</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -6399,7 +6430,9 @@
           <x:t xml:space="preserve">サービス</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -6901,7 +6934,9 @@
           <x:t xml:space="preserve">サービス</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -7379,7 +7414,9 @@
           <x:t xml:space="preserve">backlog</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
@@ -7881,7 +7918,9 @@
           <x:t xml:space="preserve">backlog</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="n"/>
+      <x:c r="D4" s="2" t="str">
+        <x:v>guidance</x:v>
+      </x:c>
       <x:c r="E4" s="2" t="n"/>
       <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rba848f97553d4a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R4da889646b504989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R282bf01e1f744b4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R94cb7510cb204998"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rf0102fce53dd4420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rffdeebf81c0e4d8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R7d78813aa63c47f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R0924dfbdbd1a48f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R52ebc4a30c2949cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R04f446dece7a42fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R1de8c5e9bd084d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R795d7e3aebc943cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R0916de4cb31a463f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="Ra74df5ee81a043ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="R38cd691886444dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R2aadafea42c94bac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R5d162be405c247e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R680678f69bef4335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R6e5b88f90553494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R2910dafe597f4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R5eb8e805ba844395"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R6f64b98152c7478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R1e5df72475a04840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R150dc668203e49a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R966386d85b0f4622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="Rf462e840372b49b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R478fbd13b749498b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R97f5fbf006694982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R7e3b7037f8884973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R1011777597ea4b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R57a4d647bf904bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R755e245a41054aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="Ra2dd2977fee64c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="Rc31820764fd24faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R529022f9deef4c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R2caff5e55e894890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="Raf0433fd6a404865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R8a45b204fe674c57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4465,8 +4465,12 @@
       <x:c r="D4" s="2" t="str">
         <x:v>guidance</x:v>
       </x:c>
-      <x:c r="E4" s="2" t="n"/>
-      <x:c r="F4" s="2" t="n"/>
+      <x:c r="E4" s="2" t="str">
+        <x:v>revenue_guidance</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="str">
+        <x:v>profit_guidance</x:v>
+      </x:c>
       <x:c r="G4" s="2" t="n"/>
       <x:c r="H4" s="2" t="n"/>
     </x:row>
@@ -4969,8 +4973,12 @@
       <x:c r="D4" s="2" t="str">
         <x:v>guidance</x:v>
       </x:c>
-      <x:c r="E4" s="2" t="n"/>
-      <x:c r="F4" s="2" t="n"/>
+      <x:c r="E4" s="2" t="str">
+        <x:v>revenue_guidance</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="str">
+        <x:v>profit_guidance</x:v>
+      </x:c>
       <x:c r="G4" s="2" t="n"/>
       <x:c r="H4" s="2" t="n"/>
     </x:row>

--- a/company_master_template.xlsx
+++ b/company_master_template.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="R2910dafe597f4a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R5eb8e805ba844395"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R6f64b98152c7478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R1e5df72475a04840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="R150dc668203e49a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="R966386d85b0f4622"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="Rf462e840372b49b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R478fbd13b749498b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R97f5fbf006694982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R7e3b7037f8884973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R1011777597ea4b31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R57a4d647bf904bc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R755e245a41054aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="Ra2dd2977fee64c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="Rc31820764fd24faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R529022f9deef4c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R2caff5e55e894890"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="Raf0433fd6a404865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R8a45b204fe674c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="1" r:id="Rba848f97553d4a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_四半期" sheetId="2" r:id="R4da889646b504989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社全体_年度" sheetId="3" r:id="R282bf01e1f744b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_四半期" sheetId="4" r:id="R94cb7510cb204998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高_年度" sheetId="5" r:id="Rf0102fce53dd4420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_四半期" sheetId="6" r:id="Rffdeebf81c0e4d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント利益_年度" sheetId="7" r:id="R7d78813aa63c47f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_四半期" sheetId="8" r:id="R0924dfbdbd1a48f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受注_年度" sheetId="9" r:id="R52ebc4a30c2949cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_四半期" sheetId="10" r:id="R04f446dece7a42fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARR_年度" sheetId="11" r:id="R1de8c5e9bd084d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_四半期" sheetId="12" r:id="R795d7e3aebc943cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セグメント売上高2_年度" sheetId="13" r:id="R0916de4cb31a463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_四半期" sheetId="14" r:id="Ra74df5ee81a043ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注高_年度" sheetId="15" r:id="R38cd691886444dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_四半期" sheetId="16" r:id="R2aadafea42c94bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品目別受注残高_年度" sheetId="17" r:id="R5d162be405c247e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全社ARR_四半期" sheetId="18" r:id="R680678f69bef4335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="製品別ARR_四半期" sheetId="19" r:id="R6e5b88f90553494a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4465,12 +4465,8 @@
       <x:c r="D4" s="2" t="str">
         <x:v>guidance</x:v>
       </x:c>
-      <x:c r="E4" s="2" t="str">
-        <x:v>revenue_guidance</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="str">
-        <x:v>profit_guidance</x:v>
-      </x:c>
+      <x:c r="E4" s="2" t="n"/>
+      <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
       <x:c r="H4" s="2" t="n"/>
     </x:row>
@@ -4973,12 +4969,8 @@
       <x:c r="D4" s="2" t="str">
         <x:v>guidance</x:v>
       </x:c>
-      <x:c r="E4" s="2" t="str">
-        <x:v>revenue_guidance</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="str">
-        <x:v>profit_guidance</x:v>
-      </x:c>
+      <x:c r="E4" s="2" t="n"/>
+      <x:c r="F4" s="2" t="n"/>
       <x:c r="G4" s="2" t="n"/>
       <x:c r="H4" s="2" t="n"/>
     </x:row>
